--- a/Meta.xlsx
+++ b/Meta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buseshualpen-my.sharepoint.com/personal/jose_vasquez_conectamobility_cl/Documents/Escritorio/Balance Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B745A6E-EAF3-4984-BE6E-B74F5C6FAF5E}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77755377-D85B-4B71-B9C3-FF0DEA927965}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,8 +99,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -484,11 +485,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -592,10 +594,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -873,13 +878,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -896,169 +901,171 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5">
+        <v>116</v>
+      </c>
+      <c r="C2" s="6">
         <v>122</v>
       </c>
-      <c r="C2" s="6">
-        <v>128</v>
-      </c>
       <c r="D2" s="26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="7">
-        <f>+SUM(B2:D2)</f>
-        <v>270</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="E2:E14" si="0">+SUM(B2:D2)</f>
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="9">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="10">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D3" s="27">
         <v>0</v>
       </c>
       <c r="E3" s="7">
-        <f>+SUM(B3:D3)</f>
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="9">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C4" s="10">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="D4" s="27">
         <v>8</v>
       </c>
       <c r="E4" s="7">
-        <f>+SUM(B4:D4)</f>
-        <v>394</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="10">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D5" s="27">
         <v>6</v>
       </c>
       <c r="E5" s="7">
-        <f>+SUM(B5:D5)</f>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="32">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" s="33">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D6" s="34">
         <v>15</v>
       </c>
       <c r="E6" s="21">
-        <f>+SUM(B6:D6)</f>
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>184</v>
+      </c>
+      <c r="H6" s="39"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="35">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" s="36">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D7" s="37">
         <v>0</v>
       </c>
       <c r="E7" s="38">
-        <f>+SUM(B7:D7)</f>
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="16">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D8" s="28">
         <v>0</v>
       </c>
       <c r="E8" s="7">
-        <f>+SUM(B8:D8)</f>
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>182</v>
+      </c>
+      <c r="H8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="17">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" s="18">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D9" s="29">
         <v>0</v>
       </c>
       <c r="E9" s="7">
-        <f>+SUM(B9:D9)</f>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="17">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C10" s="18">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D10" s="29">
         <v>0</v>
       </c>
       <c r="E10" s="7">
-        <f>+SUM(B10:D10)</f>
-        <v>286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>14</v>
       </c>
@@ -1066,35 +1073,35 @@
         <v>8</v>
       </c>
       <c r="C11" s="18">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="29">
         <v>0</v>
       </c>
       <c r="E11" s="7">
-        <f>+SUM(B11:D11)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="18">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="29">
         <v>10</v>
       </c>
       <c r="E12" s="7">
-        <f>+SUM(B12:D12)</f>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
@@ -1102,17 +1109,17 @@
         <v>1</v>
       </c>
       <c r="C13" s="18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="29">
         <v>4</v>
       </c>
       <c r="E13" s="7">
-        <f>+SUM(B13:D13)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>9</v>
       </c>
@@ -1120,17 +1127,17 @@
         <v>18</v>
       </c>
       <c r="C14" s="20">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" s="30">
         <v>10</v>
       </c>
       <c r="E14" s="7">
-        <f>+SUM(B14:D14)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>16</v>
       </c>

--- a/Meta.xlsx
+++ b/Meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buseshualpen-my.sharepoint.com/personal/jose_vasquez_conectamobility_cl/Documents/Escritorio/Balance Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77755377-D85B-4B71-B9C3-FF0DEA927965}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D121F11-D808-4DCF-BDA2-F6D7CC941327}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -906,17 +906,17 @@
         <v>5</v>
       </c>
       <c r="B2" s="5">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="C2" s="6">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D2" s="26">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E2" s="7">
-        <f t="shared" ref="E2:E14" si="0">+SUM(B2:D2)</f>
-        <v>257</v>
+        <f>+SUM(B2:D2)</f>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -924,7 +924,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="9">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C3" s="10">
         <v>57</v>
@@ -933,8 +933,8 @@
         <v>0</v>
       </c>
       <c r="E3" s="7">
-        <f t="shared" si="0"/>
-        <v>104</v>
+        <f t="shared" ref="E3:E14" si="0">+SUM(B3:D3)</f>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -942,17 +942,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="9">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C4" s="10">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="D4" s="27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="7">
         <f t="shared" si="0"/>
-        <v>376</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -960,17 +960,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="9">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C5" s="10">
-        <v>145</v>
-      </c>
-      <c r="D5" s="27">
-        <v>6</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="D5" s="27"/>
       <c r="E5" s="7">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -978,17 +976,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="32">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C6" s="33">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D6" s="34">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E6" s="21">
         <f t="shared" si="0"/>
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="H6" s="39"/>
     </row>
@@ -997,17 +995,17 @@
         <v>12</v>
       </c>
       <c r="B7" s="35">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C7" s="36">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="D7" s="37">
         <v>0</v>
       </c>
       <c r="E7" s="38">
         <f t="shared" si="0"/>
-        <v>251</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1015,17 +1013,17 @@
         <v>11</v>
       </c>
       <c r="B8" s="15">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C8" s="16">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D8" s="28">
         <v>0</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="H8" s="40"/>
     </row>
@@ -1034,17 +1032,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="17">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C9" s="18">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D9" s="29">
         <v>0</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1052,17 +1050,17 @@
         <v>10</v>
       </c>
       <c r="B10" s="17">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C10" s="18">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="D10" s="29">
         <v>0</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" si="0"/>
-        <v>272</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1073,14 +1071,14 @@
         <v>8</v>
       </c>
       <c r="C11" s="18">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D11" s="29">
         <v>0</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1088,17 +1086,17 @@
         <v>15</v>
       </c>
       <c r="B12" s="17">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C12" s="18">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D12" s="29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1106,17 +1104,17 @@
         <v>17</v>
       </c>
       <c r="B13" s="17">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C13" s="18">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D13" s="29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1124,17 +1122,17 @@
         <v>9</v>
       </c>
       <c r="B14" s="19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="20">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Meta.xlsx
+++ b/Meta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buseshualpen-my.sharepoint.com/personal/jose_vasquez_conectamobility_cl/Documents/Escritorio/Balance Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D121F11-D808-4DCF-BDA2-F6D7CC941327}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABB53C1-563A-4D19-A01A-E8D487870A4F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -906,17 +906,17 @@
         <v>5</v>
       </c>
       <c r="B2" s="5">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C2" s="6">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="D2" s="26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="7">
         <f>+SUM(B2:D2)</f>
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -924,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="9">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C3" s="10">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" s="27">
         <v>0</v>
@@ -942,17 +942,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="9">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="C4" s="10">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="D4" s="27">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E4" s="7">
         <f t="shared" si="0"/>
-        <v>395</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -960,15 +960,17 @@
         <v>7</v>
       </c>
       <c r="B5" s="9">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C5" s="10">
-        <v>97</v>
-      </c>
-      <c r="D5" s="27"/>
+        <v>96</v>
+      </c>
+      <c r="D5" s="27">
+        <v>29</v>
+      </c>
       <c r="E5" s="7">
         <f t="shared" si="0"/>
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -976,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="32">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="33">
         <v>104</v>
@@ -986,7 +988,7 @@
       </c>
       <c r="E6" s="21">
         <f t="shared" si="0"/>
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H6" s="39"/>
     </row>
@@ -995,17 +997,17 @@
         <v>12</v>
       </c>
       <c r="B7" s="35">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C7" s="36">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D7" s="37">
         <v>0</v>
       </c>
       <c r="E7" s="38">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1013,17 +1015,17 @@
         <v>11</v>
       </c>
       <c r="B8" s="15">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C8" s="16">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="D8" s="28">
         <v>0</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="H8" s="40"/>
     </row>
@@ -1032,17 +1034,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="17">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C9" s="18">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D9" s="29">
         <v>0</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v>265</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1050,10 +1052,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="17">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C10" s="18">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="D10" s="29">
         <v>0</v>
@@ -1068,17 +1070,17 @@
         <v>14</v>
       </c>
       <c r="B11" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C11" s="18">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D11" s="29">
         <v>0</v>
       </c>
       <c r="E11" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1089,14 +1091,14 @@
         <v>14</v>
       </c>
       <c r="C12" s="18">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12" s="29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1104,17 +1106,17 @@
         <v>17</v>
       </c>
       <c r="B13" s="17">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C13" s="18">
         <v>21</v>
       </c>
       <c r="D13" s="29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1122,17 +1124,17 @@
         <v>9</v>
       </c>
       <c r="B14" s="19">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14" s="20">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D14" s="30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Meta.xlsx
+++ b/Meta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buseshualpen-my.sharepoint.com/personal/jose_vasquez_conectamobility_cl/Documents/Escritorio/Balance Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BABB53C1-563A-4D19-A01A-E8D487870A4F}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="11_AD4D2F04E46CFB4ACB3E2035C5D5E230683EDF10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C4151AC-C10A-4FA7-BB68-89296FC6F416}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -906,17 +906,17 @@
         <v>5</v>
       </c>
       <c r="B2" s="5">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C2" s="6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" s="26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7">
         <f>+SUM(B2:D2)</f>
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -924,17 +924,17 @@
         <v>8</v>
       </c>
       <c r="B3" s="9">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3" s="10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="27">
         <v>0</v>
       </c>
       <c r="E3" s="7">
         <f t="shared" ref="E3:E14" si="0">+SUM(B3:D3)</f>
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -942,17 +942,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="9">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C4" s="10">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="D4" s="27">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E4" s="7">
         <f t="shared" si="0"/>
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -963,14 +963,14 @@
         <v>49</v>
       </c>
       <c r="C5" s="10">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D5" s="27">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7">
         <f t="shared" si="0"/>
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -978,17 +978,17 @@
         <v>4</v>
       </c>
       <c r="B6" s="32">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6" s="33">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D6" s="34">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E6" s="21">
         <f t="shared" si="0"/>
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H6" s="39"/>
     </row>
@@ -997,7 +997,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="35">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7" s="36">
         <v>240</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E7" s="38">
         <f t="shared" si="0"/>
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1015,17 +1015,17 @@
         <v>11</v>
       </c>
       <c r="B8" s="15">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="16">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D8" s="28">
         <v>0</v>
       </c>
       <c r="E8" s="7">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H8" s="40"/>
     </row>
@@ -1034,17 +1034,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="17">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C9" s="18">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D9" s="29">
         <v>0</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1052,17 +1052,17 @@
         <v>10</v>
       </c>
       <c r="B10" s="17">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C10" s="18">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="D10" s="29">
         <v>0</v>
       </c>
       <c r="E10" s="7">
         <f t="shared" si="0"/>
-        <v>297</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1070,10 +1070,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="18">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="29">
         <v>0</v>
@@ -1088,17 +1088,17 @@
         <v>15</v>
       </c>
       <c r="B12" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" s="18">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D12" s="29">
         <v>0</v>
       </c>
       <c r="E12" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1106,10 +1106,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="29">
         <v>0</v>
@@ -1124,17 +1124,17 @@
         <v>9</v>
       </c>
       <c r="B14" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C14" s="20">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" s="30">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
